--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="2" r:id="rId1"/>
-    <sheet name="Update" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -255,236 +254,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>作者</author>
-    <author>郭娟</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Question title
-问题标题</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Difficulty Level
-1: Easy
-2: Moderate
-3: Difficult
-4: Very difficult
-问题难度：
-1:简单
-2:一般
-3:较难
-4:困难</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Question type
-题目类型
-0: Muiltple choice
-0: 单选题
-1: Checkboxes
-1: 多选题</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Answer
-答案
-Muiltple choice, One question only, sample: A
-单选，只能设置一个答案，如：A
-Checkboxes, More than one question, sample: A|B
-多选，可设置多个答案任意组合，如：A|B</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option A
-选项 A</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option B
-选项 B</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option C
-选项 C</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option D
-选项 D</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option E
-选项 E</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option F
-选项 F</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option G
-选项 G</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option H
-选项 H</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option I
-选项 I</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Option J
-选项 J</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>Title</t>
   </si>
@@ -549,67 +320,25 @@
     <t>2nd Cutting</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Bagaimana cara mencegah jamur pada produk ?</t>
-  </si>
-  <si>
-    <t>Tidak makan dan minum di area kerja saat bersentuhan dengan produk</t>
-  </si>
-  <si>
-    <t>Tidak menggunakan air untuk membersihkan produk tanpa izin</t>
-  </si>
-  <si>
-    <t>Mengimplementasikan sistem 6S</t>
-  </si>
-  <si>
-    <t>Semua Jawaban Benar</t>
-  </si>
-  <si>
-    <t>Berikut ini yang bukan termasuk dalam aktivitas Ironware Management adalah?</t>
-  </si>
-  <si>
-    <t>Pengendalian Peralatan Metal</t>
-  </si>
-  <si>
-    <t>Broken Needle Policy</t>
-  </si>
-  <si>
-    <t>Metal Detector Policy</t>
-  </si>
-  <si>
-    <t>Error Proofing</t>
-  </si>
-  <si>
-    <t>Apa tujuan dari BNP ?</t>
-  </si>
-  <si>
-    <t>Mencegah patahan jarum sampai ke konsumen</t>
-  </si>
-  <si>
-    <t>Mencegah jamur tumbuh pada produk</t>
-  </si>
-  <si>
-    <t>Mencegah issue bonding pada Produk</t>
-  </si>
-  <si>
-    <t>Mencegah Reinspect</t>
-  </si>
-  <si>
-    <t>Sistem management yang mencegah resiko produk dengan isu terkirim atau membahayakan customer adalah?</t>
-  </si>
-  <si>
-    <t>Zero Tolerance Management</t>
-  </si>
-  <si>
-    <t>MPPA</t>
-  </si>
-  <si>
-    <t>MI Score</t>
-  </si>
-  <si>
-    <t>PFC</t>
+    <t>Apakakah Ironware management termasuk kedalam Zero Tolerance?</t>
+  </si>
+  <si>
+    <t>Binary</t>
+  </si>
+  <si>
+    <t>Ya</t>
+  </si>
+  <si>
+    <t>Tidak</t>
+  </si>
+  <si>
+    <t>Apakah benar perlatan besi/gunting harus diletakkan di Toolbox management?</t>
+  </si>
+  <si>
+    <t>Apakah benar fungsi dari natural cooling adalah untuk menghilangkan kelembapan yang ada di sepatu?</t>
+  </si>
+  <si>
+    <t>Apakah benar jika Over buffing, Rocking, Off center merupakan contoh issue dalam MPPA yang masuk kedalam kategori severe?</t>
   </si>
 </sst>
 </file>
@@ -794,18 +523,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1124,7 +847,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1148,16 +871,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1166,92 +889,91 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1601,10 +1323,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="159.161904761905" style="1" customWidth="1"/>
+    <col min="1" max="1" width="53.5714285714286" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.8285714285714" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.16190476190476" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.16190476190476" style="1" customWidth="1"/>
@@ -1665,7 +1387,7 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1">
@@ -1688,6 +1410,86 @@
       </c>
       <c r="I2" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1696,187 +1498,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
-  <cols>
-    <col min="1" max="1" width="116.714285714286" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="6.14285714285714" customWidth="1"/>
-    <col min="4" max="4" width="8.57142857142857" customWidth="1"/>
-    <col min="5" max="5" width="22.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="74.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="65.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="40.1428571428571" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="3" customWidth="1"/>
-    <col min="11" max="11" width="2.85714285714286" customWidth="1"/>
-    <col min="12" max="12" width="3.14285714285714" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="2.57142857142857" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.25" customHeight="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>